--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104554_W11.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104554_W11.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1839</v>
+        <v>7.1922</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7779</v>
+        <v>6.4389</v>
       </c>
       <c r="F2" t="n">
-        <v>0.406</v>
+        <v>0.7533</v>
       </c>
       <c r="G2" t="n">
-        <v>6.7253</v>
+        <v>6.7114</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6147</v>
+        <v>3.6104</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1106</v>
+        <v>3.101</v>
       </c>
       <c r="J2" t="n">
-        <v>7.5796</v>
+        <v>7.5424</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4504</v>
+        <v>4.4299</v>
       </c>
       <c r="L2" t="n">
-        <v>3.1292</v>
+        <v>3.1126</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.831</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8357</v>
+        <v>-0.8194</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5414</v>
+        <v>0.4809</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6261</v>
+        <v>0.0834</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0847</v>
+        <v>0.3975</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.24</v>
+        <v>2.519</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0743</v>
+        <v>2.368</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1657</v>
+        <v>0.151</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7823</v>
+        <v>4.0891</v>
       </c>
       <c r="H3" t="n">
-        <v>0.14</v>
+        <v>-0.2958</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6424</v>
+        <v>4.385</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2784</v>
+        <v>4.7491</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8733</v>
+        <v>1.0407</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4051</v>
+        <v>3.7083</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.496</v>
+        <v>-0.6599</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7334</v>
+        <v>-1.3365</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2373</v>
+        <v>0.6766</v>
       </c>
       <c r="P3" t="n">
-        <v>1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4952</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4823</v>
+        <v>0.1127</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3157</v>
+        <v>-0.0561</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1666</v>
+        <v>0.1688</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3856</v>
+        <v>-0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3856</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3572</v>
+        <v>2.4665</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1915</v>
+        <v>0.9774</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1657</v>
+        <v>1.4891</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.1772</v>
+        <v>0.7827</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1083</v>
+        <v>0.1407</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0689</v>
+        <v>0.642</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.2401</v>
+        <v>2.2451</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1834</v>
+        <v>1.8508</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.4234</v>
+        <v>0.3943</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9371</v>
+        <v>-1.4624</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2917</v>
+        <v>-1.7102</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3546</v>
+        <v>0.2477</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>2.5039</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0956</v>
+        <v>0.705</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8075</v>
+        <v>0.2574</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2881</v>
+        <v>0.4476</v>
       </c>
       <c r="V4" t="n">
-        <v>2.8924</v>
+        <v>-0.387</v>
       </c>
       <c r="W4" t="n">
-        <v>2.8924</v>
+        <v>-0.387</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8983</v>
+        <v>1.7484</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3626</v>
+        <v>-0.2612</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2609</v>
+        <v>2.0097</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5663</v>
+        <v>-0.5598</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3506</v>
+        <v>0.3531</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9169</v>
+        <v>-0.913</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4721</v>
+        <v>0.4568</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9973</v>
+        <v>0.9858</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5251</v>
+        <v>-0.529</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0384</v>
+        <v>-1.0166</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1213</v>
+        <v>-0.2867</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8347</v>
+        <v>-0.718</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7134</v>
+        <v>0.4313</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6675</v>
+        <v>1.286</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7107</v>
+        <v>-0.3108</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0432</v>
+        <v>1.5968</v>
       </c>
       <c r="G6" t="n">
-        <v>4.0996</v>
+        <v>-2.1727</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2958</v>
+        <v>-1.1032</v>
       </c>
       <c r="I6" t="n">
-        <v>4.3954</v>
+        <v>-1.0696</v>
       </c>
       <c r="J6" t="n">
-        <v>4.7857</v>
+        <v>-1.2547</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0594</v>
+        <v>0.1756</v>
       </c>
       <c r="L6" t="n">
-        <v>3.7263</v>
+        <v>-1.4303</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6861</v>
+        <v>-0.918</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3552</v>
+        <v>-1.2788</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6691</v>
+        <v>0.3608</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1342</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2683</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7516</v>
+        <v>1.0325</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7652</v>
+        <v>0.3388</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0136</v>
+        <v>0.6937</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5463</v>
+        <v>2.8814</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>2.8814</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3613</v>
+        <v>0.5111</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4422</v>
+        <v>0.5243</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0809</v>
+        <v>-0.0133</v>
       </c>
       <c r="G7" t="n">
-        <v>0.251</v>
+        <v>0.2403</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3648</v>
+        <v>-0.3811</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6158</v>
+        <v>0.6214</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0467</v>
+        <v>1.0149</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7855</v>
+        <v>0.7542</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2612</v>
+        <v>0.2607</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7957</v>
+        <v>-0.7745</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1503</v>
+        <v>-1.1353</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4564</v>
+        <v>0.6075</v>
       </c>
       <c r="T7" t="n">
-        <v>0.369</v>
+        <v>0.4899</v>
       </c>
       <c r="U7" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.1176</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2411</v>
+        <v>-0.4907</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1457</v>
+        <v>-1.1643</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9046</v>
+        <v>0.6737</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.47</v>
+        <v>-1.4723</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7632</v>
+        <v>-1.7689</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2932</v>
+        <v>0.2966</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4732</v>
+        <v>-1.4871</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.5106</v>
+        <v>-1.5243</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0033</v>
+        <v>0.0148</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0641</v>
+        <v>-0.3159</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7652</v>
+        <v>-0.7667</v>
       </c>
       <c r="U8" t="n">
-        <v>0.701</v>
+        <v>0.4509</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.851</v>
+        <v>-0.7089</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4682</v>
+        <v>1.5612</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3193</v>
+        <v>-2.2701</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0404</v>
+        <v>2.0321</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6464</v>
+        <v>-0.649</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6868</v>
+        <v>2.6811</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2284</v>
+        <v>3.2082</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5817</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>2.6468</v>
+        <v>2.6361</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.188</v>
+        <v>-1.1761</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2281</v>
+        <v>-1.221</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3451</v>
+        <v>-0.1963</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6261</v>
+        <v>-0.5089</v>
       </c>
       <c r="U9" t="n">
-        <v>0.281</v>
+        <v>0.3126</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9344</v>
+        <v>-0.7156</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0994</v>
+        <v>0.0183</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.835</v>
+        <v>-0.7339</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0152</v>
+        <v>-1.0094</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.658</v>
+        <v>-0.655</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3572</v>
+        <v>-0.3544</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1093</v>
+        <v>0.1089</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1245</v>
+        <v>-1.1184</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6927</v>
+        <v>-0.6895</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1461</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2087</v>
+        <v>-0.0907</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0626</v>
+        <v>0.1568</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.543</v>
+        <v>-1.209</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5709</v>
+        <v>-1.4766</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0279</v>
+        <v>0.2676</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9058</v>
+        <v>-0.9081</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3882</v>
+        <v>-1.3845</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4824</v>
+        <v>0.4764</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1677</v>
+        <v>0.1521</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6478</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8156</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0735</v>
+        <v>-1.0603</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6372</v>
+        <v>-0.3009</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7652</v>
+        <v>-0.6483</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1279</v>
+        <v>0.3474</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9513</v>
+        <v>-5.4247</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8075</v>
+        <v>-3.2944</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1438</v>
+        <v>-2.1303</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5804</v>
+        <v>-1.5826</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2396</v>
+        <v>-0.2357</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3408</v>
+        <v>-1.3469</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1864</v>
+        <v>-1.1945</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3117</v>
+        <v>0.3103</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5513</v>
+        <v>-0.546</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4023</v>
+        <v>-0.0697</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6472</v>
+        <v>0.1765</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.245</v>
+        <v>-0.2462</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.187400000000002</v>
+        <v>7.174300000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>5.678700000000002</v>
+        <v>5.380800000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5086</v>
+        <v>1.7936</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1837</v>
+        <v>6.150699999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.359</v>
+        <v>-2.369</v>
       </c>
       <c r="I13" t="n">
-        <v>8.5428</v>
+        <v>8.519599999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>15.7682</v>
+        <v>15.5412</v>
       </c>
       <c r="K13" t="n">
-        <v>8.1189</v>
+        <v>7.9779</v>
       </c>
       <c r="L13" t="n">
-        <v>7.649500000000001</v>
+        <v>7.563500000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.584299999999999</v>
+        <v>-9.390499999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.4781</v>
+        <v>-10.3467</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8935000000000002</v>
+        <v>0.956</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1341</v>
+        <v>1.138099999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.7442</v>
+        <v>-14.7962</v>
       </c>
       <c r="R13" t="n">
-        <v>15.8783</v>
+        <v>15.9342</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8298</v>
+        <v>1.8353</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4518</v>
+        <v>-1.4427</v>
       </c>
       <c r="U13" t="n">
-        <v>3.2813</v>
+        <v>3.278</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.9604</v>
+        <v>-1.9497</v>
       </c>
       <c r="W13" t="n">
-        <v>6.1063</v>
+        <v>6.0785</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.066700000000001</v>
+        <v>-8.0282</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4409</v>
+        <v>2.1857</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2743</v>
+        <v>2.506</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8334</v>
+        <v>-0.3203</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.2323</v>
+        <v>-1.2374</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9957</v>
+        <v>1.9906</v>
       </c>
       <c r="I14" t="n">
         <v>-3.228</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1674</v>
+        <v>1.1277</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4145</v>
+        <v>3.3849</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.2471</v>
+        <v>-2.2572</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3996</v>
+        <v>-2.3651</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4188</v>
+        <v>-1.3943</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1437</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.617</v>
+        <v>-0.0887</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4733</v>
+        <v>-0.0055</v>
       </c>
       <c r="V14" t="n">
-        <v>4.21</v>
+        <v>4.2001</v>
       </c>
       <c r="W14" t="n">
-        <v>3.9851</v>
+        <v>3.9709</v>
       </c>
       <c r="X14" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="15">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2308</v>
+        <v>1.2418</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0325</v>
+        <v>-0.0332</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2634</v>
+        <v>1.2751</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4989</v>
+        <v>0.5078</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.482</v>
+        <v>-0.477</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9809</v>
+        <v>0.9848</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1066</v>
+        <v>0.1062</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3923</v>
+        <v>0.4016</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5513</v>
+        <v>-0.546</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9436</v>
+        <v>0.9476</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0514</v>
+        <v>0.0512</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1905</v>
+        <v>0.1906</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5992</v>
+        <v>0.9536</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9123</v>
+        <v>2.1193</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.313</v>
+        <v>-1.1657</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2892</v>
+        <v>0.2903</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0302</v>
+        <v>1.0338</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.741</v>
+        <v>-0.7433999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1726</v>
+        <v>2.1531</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9914</v>
+        <v>1.9822</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1812</v>
+        <v>0.1708</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8834</v>
+        <v>-1.8628</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4216</v>
+        <v>-0.0604</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5383</v>
+        <v>-0.3022</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1167</v>
+        <v>0.2418</v>
       </c>
       <c r="V16" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W16" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5734</v>
+        <v>0.7448</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2813</v>
+        <v>2.6125</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7078</v>
+        <v>-1.8678</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2813</v>
+        <v>0.2849</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6998</v>
+        <v>0.7035</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4185</v>
+        <v>-0.4186</v>
       </c>
       <c r="J17" t="n">
-        <v>3.116</v>
+        <v>3.0936</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3378</v>
+        <v>2.327</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7782</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8347</v>
+        <v>-2.8087</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.638</v>
+        <v>-1.6235</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1615</v>
+        <v>0.0046</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6079</v>
+        <v>-0.2535</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4464</v>
+        <v>0.2581</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. TOMIC</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3939</v>
+        <v>0.1311</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6933</v>
+        <v>0.406</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2994</v>
+        <v>-0.2748</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7159</v>
+        <v>0.4759</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1317</v>
+        <v>0.9676</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8476</v>
+        <v>-0.4917</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3725</v>
+        <v>0.5873</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2979</v>
+        <v>0.3792</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0746</v>
+        <v>0.2081</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0884</v>
+        <v>-0.1114</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1662</v>
+        <v>0.5884</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9222</v>
+        <v>-0.6998</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>2.4008</v>
+        <v>-0.0975</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3338</v>
+        <v>-0.1813</v>
       </c>
       <c r="U18" t="n">
-        <v>1.067</v>
+        <v>0.0838</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6105</v>
+        <v>-0.7025</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4822</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>A. TOMIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2367</v>
+        <v>-1.0559</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1821</v>
+        <v>-0.5414</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4188</v>
+        <v>-0.5145</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4745</v>
+        <v>-0.7322</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9624</v>
+        <v>0.1076</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4878</v>
+        <v>-0.8398</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5995</v>
+        <v>1.3318</v>
       </c>
       <c r="K19" t="n">
-        <v>0.381</v>
+        <v>1.2573</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2185</v>
+        <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1249</v>
+        <v>-2.064</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5814</v>
+        <v>-1.1497</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7063</v>
+        <v>-0.9143</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4579</v>
+        <v>0.9754</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4174</v>
+        <v>0.1574</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0405</v>
+        <v>0.8179</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7071</v>
+        <v>-0.6162</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.4733</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.7071</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. VIVES</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4457</v>
+        <v>-1.1208</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0375</v>
+        <v>-1.619</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5918</v>
+        <v>0.4982</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9364</v>
+        <v>-2.5109</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3233</v>
+        <v>-0.9187</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6131</v>
+        <v>-1.5922</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6251</v>
+        <v>-0.651</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0866</v>
+        <v>-0.3005</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7117</v>
+        <v>-0.3505</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3113</v>
+        <v>-1.8599</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4099</v>
+        <v>-0.6182</v>
       </c>
       <c r="O20" t="n">
-        <v>0.09859999999999999</v>
+        <v>-1.2417</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>2.5039</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5093</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2782</v>
+        <v>-0.6415</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2311</v>
+        <v>0.0119</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.792</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.9497</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>G. VIVES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6439</v>
+        <v>-1.3156</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0432</v>
+        <v>-2.046</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3993</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.5085</v>
+        <v>-0.9301</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9118000000000001</v>
+        <v>-0.3163</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5966</v>
+        <v>-0.6138</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6223</v>
+        <v>-0.629</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2811</v>
+        <v>0.0862</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3413</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8861</v>
+        <v>-0.3011</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6308</v>
+        <v>-0.4025</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2554</v>
+        <v>0.1014</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4952</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.162</v>
+        <v>-0.3856</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.113</v>
+        <v>-0.2788</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.049</v>
+        <v>-0.1067</v>
       </c>
       <c r="V21" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.9604</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7093</v>
+        <v>-1.7365</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0571</v>
+        <v>-0.717</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6522</v>
+        <v>-1.0195</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0234</v>
+        <v>0.0383</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.5134</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4771</v>
+        <v>-0.4751</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1204</v>
+        <v>1.1114</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6754</v>
+        <v>0.6722</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0971</v>
+        <v>-1.0731</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1749</v>
+        <v>-0.1588</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.362</v>
+        <v>-0.4169</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0434</v>
+        <v>-0.6902</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6814</v>
+        <v>0.2733</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.587</v>
+        <v>-2.2668</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0129</v>
+        <v>-0.7846</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5741</v>
+        <v>-1.4822</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.7992</v>
+        <v>-2.7835</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3839</v>
+        <v>-1.3762</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.4153</v>
+        <v>-1.4073</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0391</v>
+        <v>-0.0457</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0764</v>
+        <v>-0.0829</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.7602</v>
+        <v>-2.7378</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3075</v>
+        <v>-1.2932</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P23" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8293</v>
+        <v>-0.532</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.747</v>
+        <v>-0.5113</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0823</v>
+        <v>-0.0207</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8028</v>
+        <v>-4.9356</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6684</v>
+        <v>-3.696</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1344</v>
+        <v>-1.2395</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4412</v>
+        <v>0.4463</v>
       </c>
       <c r="H24" t="n">
-        <v>0.14</v>
+        <v>0.1407</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3012</v>
+        <v>0.3056</v>
       </c>
       <c r="J24" t="n">
-        <v>1.216</v>
+        <v>1.2051</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5817</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7749</v>
+        <v>-0.7588</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.522</v>
+        <v>-0.6502</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3478</v>
+        <v>-0.3485</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1742</v>
+        <v>-0.3017</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.1872</v>
+        <v>-7.174200000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.508300000000001</v>
+        <v>-1.793400000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.6786</v>
+        <v>-5.380700000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.1838</v>
+        <v>-6.1506</v>
       </c>
       <c r="H25" t="n">
-        <v>2.359300000000001</v>
+        <v>2.369</v>
       </c>
       <c r="I25" t="n">
-        <v>-8.542899999999999</v>
+        <v>-8.519500000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>9.5845</v>
+        <v>9.390499999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>10.4781</v>
+        <v>10.3466</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.8934999999999998</v>
+        <v>-0.9563000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-15.7683</v>
+        <v>-15.5411</v>
       </c>
       <c r="N25" t="n">
-        <v>-8.1189</v>
+        <v>-7.9777</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.6493</v>
+        <v>-7.5635</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.1341</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q25" t="n">
-        <v>-15.8784</v>
+        <v>-15.9341</v>
       </c>
       <c r="R25" t="n">
-        <v>14.7444</v>
+        <v>14.7962</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.8297</v>
+        <v>-1.8351</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.281299999999999</v>
+        <v>-3.278</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4516</v>
+        <v>1.4428</v>
       </c>
       <c r="V25" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="W25" t="n">
-        <v>8.066700000000001</v>
+        <v>8.0281</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.1063</v>
+        <v>-6.0785</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104554_W11.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104554_W11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.0282</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104554_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-6.0785</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
